--- a/data/trans_orig/KIDM_C_2_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_2_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>25112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73323</t>
+          <t>72474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48122</t>
+          <t>47940</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53031</t>
+          <t>53051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97031</t>
+          <t>96715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>102186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146846</t>
+          <t>147275</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154246</t>
+          <t>154498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67556</t>
+          <t>67696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57426</t>
+          <t>56738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64149</t>
+          <t>64145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127155</t>
+          <t>126756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136128</t>
+          <t>135928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50888</t>
+          <t>51732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104487</t>
+          <t>104614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200011</t>
+          <t>199979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208375</t>
+          <t>208436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>260071</t>
+          <t>259755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>269297</t>
+          <t>269356</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>463375</t>
+          <t>463707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>475939</t>
+          <t>475957</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
